--- a/validation/expert_reviews/E3_extraction_review.xlsx
+++ b/validation/expert_reviews/E3_extraction_review.xlsx
@@ -580,7 +580,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Review workbook — Angelina</t>
+          <t>Review workbook — E3</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E3    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Angelina</t>
+          <t>Rating — E3</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E3    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Angelina</t>
+          <t>Rating — E3</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E3    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Angelina</t>
+          <t>Rating — E3</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E3    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Angelina</t>
+          <t>Rating — E3</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E3    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Angelina</t>
+          <t>Rating — E3</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E3    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Angelina</t>
+          <t>Rating — E3</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E3    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4240,6 +4240,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4355,6 +4356,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -4697,7 +4699,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E3    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4757,6 +4759,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4872,6 +4875,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5214,7 +5218,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E3    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5274,6 +5278,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5389,6 +5394,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5731,7 +5737,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E3    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5791,6 +5797,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5906,6 +5913,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6248,7 +6256,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E3    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -6308,6 +6316,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -6423,6 +6432,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6765,7 +6775,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E3    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -6825,6 +6835,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -6940,6 +6951,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -7282,7 +7294,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E3    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -7342,6 +7354,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -7457,6 +7470,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -7804,7 +7818,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Angelina    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E3    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7837,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Angelina</t>
+          <t>Rating — E3</t>
         </is>
       </c>
     </row>
